--- a/data/majors_info.xlsx
+++ b/data/majors_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20343"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D167DA-F869-4173-AD26-8D2CA8ECB37F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07413668-A59D-4ECC-881A-23C7C04E336E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -789,11 +789,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>컴퓨터, 네트워크, 프로그래밍 등 전공을 위한 기본 기술을 습득 하고, 정보시스템, 정보네트워크의 보안 관리, 해킹 및 대응방법 등
-정보보안 분야에 특성화된 실무처리능력을 배양하여 시스템 관리자, 시스템 개발자, 보안전문가, 보안사고분석 전문가 등을 양성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>평캠 인학관 303호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1058,11 +1053,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>정보보안전공(평캠)</t>
+    <t>컴퓨터공학전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>컴퓨터공학전공</t>
+    <t>정보보안전공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터, 네트워크, 프로그래밍 등 전공을 위한 기본 기술을 습득 하고, 정보시스템, 정보네트워크의 보안 관리, 해킹 및 대응방법 등 정보보안 분야에 특성화된 실무처리능력을 배양하여 시스템 관리자, 시스템 개발자, 보안전문가, 보안사고분석 전문가 등을 양성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1510,7 +1509,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
@@ -1536,7 +1535,7 @@
         <v>87</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>35</v>
@@ -1562,7 +1561,7 @@
         <v>83</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>35</v>
@@ -1588,7 +1587,7 @@
         <v>70</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>35</v>
@@ -1614,7 +1613,7 @@
         <v>82</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>35</v>
@@ -1640,7 +1639,7 @@
         <v>81</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>35</v>
@@ -1666,7 +1665,7 @@
         <v>90</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>35</v>
@@ -1692,7 +1691,7 @@
         <v>94</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>35</v>
@@ -1718,7 +1717,7 @@
         <v>97</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>35</v>
@@ -1744,7 +1743,7 @@
         <v>99</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>35</v>
@@ -1770,7 +1769,7 @@
         <v>102</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>35</v>
@@ -1796,7 +1795,7 @@
         <v>107</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>35</v>
@@ -1822,7 +1821,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>35</v>
@@ -1848,7 +1847,7 @@
         <v>114</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>35</v>
@@ -1874,7 +1873,7 @@
         <v>117</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>35</v>
@@ -1900,7 +1899,7 @@
         <v>121</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>35</v>
@@ -1926,7 +1925,7 @@
         <v>124</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>35</v>
@@ -1952,7 +1951,7 @@
         <v>131</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>35</v>
@@ -1978,7 +1977,7 @@
         <v>128</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>35</v>
@@ -2004,7 +2003,7 @@
         <v>71</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>35</v>
@@ -2030,7 +2029,7 @@
         <v>197</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>35</v>
@@ -2047,7 +2046,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>134</v>
@@ -2056,7 +2055,7 @@
         <v>138</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>35</v>
@@ -2082,7 +2081,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>35</v>
@@ -2102,13 +2101,13 @@
         <v>267</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>35</v>
@@ -2120,7 +2119,7 @@
         <v>199</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2134,7 +2133,7 @@
         <v>141</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>35</v>
@@ -2160,7 +2159,7 @@
         <v>145</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>35</v>
@@ -2186,7 +2185,7 @@
         <v>148</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>35</v>
@@ -2212,7 +2211,7 @@
         <v>152</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>35</v>
@@ -2238,7 +2237,7 @@
         <v>154</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>35</v>
@@ -2255,7 +2254,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>156</v>
@@ -2264,7 +2263,7 @@
         <v>157</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>35</v>
@@ -2290,7 +2289,7 @@
         <v>161</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>35</v>
@@ -2316,7 +2315,7 @@
         <v>183</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>35</v>
@@ -2333,7 +2332,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>179</v>
@@ -2342,7 +2341,7 @@
         <v>180</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>35</v>
@@ -2359,7 +2358,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>185</v>
@@ -2368,13 +2367,13 @@
         <v>186</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>178</v>
@@ -2385,7 +2384,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>188</v>
@@ -2394,13 +2393,13 @@
         <v>72</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>178</v>
@@ -2411,7 +2410,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>190</v>
@@ -2420,7 +2419,7 @@
         <v>191</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>35</v>
@@ -2437,215 +2436,215 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B37" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="D37" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G37" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>204</v>
-      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>217</v>
-      </c>
       <c r="D38" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B39" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>219</v>
-      </c>
       <c r="D39" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B40" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="D40" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>224</v>
-      </c>
       <c r="D41" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F41" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>222</v>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>250</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B42" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>228</v>
-      </c>
       <c r="D42" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H42" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B43" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>231</v>
-      </c>
       <c r="D43" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F43" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>234</v>
-      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B44" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>237</v>
-      </c>
       <c r="D44" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>165</v>
@@ -2654,10 +2653,10 @@
         <v>166</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>68</v>
@@ -2671,7 +2670,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>163</v>
@@ -2680,10 +2679,10 @@
         <v>164</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>68</v>
@@ -2697,7 +2696,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>167</v>
@@ -2706,10 +2705,10 @@
         <v>168</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>68</v>
@@ -2723,7 +2722,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>169</v>
@@ -2732,10 +2731,10 @@
         <v>170</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>68</v>
@@ -2749,7 +2748,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>171</v>
@@ -2758,10 +2757,10 @@
         <v>172</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>68</v>
@@ -2775,7 +2774,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>173</v>
@@ -2784,10 +2783,10 @@
         <v>174</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>68</v>
@@ -2801,7 +2800,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>175</v>
@@ -2810,10 +2809,10 @@
         <v>176</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>68</v>

--- a/data/majors_info.xlsx
+++ b/data/majors_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07413668-A59D-4ECC-881A-23C7C04E336E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70412E3B-702B-4379-A8BF-05817C0F658F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>031-670-5200</t>
-  </si>
-  <si>
-    <t>031-670-4820</t>
   </si>
   <si>
     <t>031-670-5340</t>
@@ -697,10 +694,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>대학본부 103호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.hknu.ac.kr/art/index.do#this</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -789,31 +782,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>평캠 인학관 303호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>컴퓨터, 네트워크, 정보, 보안, 프로그래밍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>https://www.hknu.ac.kr/welfare/index.do</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인학관A동 513호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인학관B동 503호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인학관B동 604호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인학관A동 616호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -826,18 +799,6 @@
   </si>
   <si>
     <t>031-610-4840</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>031-671-4790</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>031-671-4961</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>031-671-4811</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -945,10 +906,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>031-671-4830</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>시각미디어디자인전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1033,22 +990,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예체능 계열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인문사회 계열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자연과학 계열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공학 계열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>건축학전공(5년제)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1062,6 +1003,66 @@
   </si>
   <si>
     <t>컴퓨터, 네트워크, 프로그래밍 등 전공을 위한 기본 기술을 습득 하고, 정보시스템, 정보네트워크의 보안 관리, 해킹 및 대응방법 등 정보보안 분야에 특성화된 실무처리능력을 배양하여 시스템 관리자, 시스템 개발자, 보안전문가, 보안사고분석 전문가 등을 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-8046-4020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제2공학관 205호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-610-4830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평캠 인학관A동 513호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평캠 인학관B동 503호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평캠 인학관B동 604호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평캠 인학관A동 616호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-610-4790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-610-4961</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>031-610-4811</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공학계열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예체능계열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인문사회계열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연과학계열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생성공관 701호(대학원통합행정실)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1509,7 +1510,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
@@ -1529,13 +1530,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>35</v>
@@ -1544,10 +1545,10 @@
         <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1555,13 +1556,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>35</v>
@@ -1570,10 +1571,10 @@
         <v>37</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1581,13 +1582,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>35</v>
@@ -1596,10 +1597,10 @@
         <v>38</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1607,13 +1608,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>35</v>
@@ -1622,10 +1623,10 @@
         <v>39</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1633,13 +1634,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="D6" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>35</v>
@@ -1648,10 +1649,10 @@
         <v>40</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1659,13 +1660,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="D7" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>35</v>
@@ -1674,10 +1675,10 @@
         <v>41</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1685,13 +1686,13 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="D8" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>35</v>
@@ -1700,10 +1701,10 @@
         <v>42</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1711,13 +1712,13 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>35</v>
@@ -1726,10 +1727,10 @@
         <v>43</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1737,13 +1738,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>99</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>35</v>
@@ -1752,10 +1753,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1763,13 +1764,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>35</v>
@@ -1778,10 +1779,10 @@
         <v>45</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1789,13 +1790,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>107</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>35</v>
@@ -1804,10 +1805,10 @@
         <v>46</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1815,13 +1816,13 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="D13" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>35</v>
@@ -1830,10 +1831,10 @@
         <v>47</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1841,10 +1842,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>264</v>
@@ -1856,10 +1857,10 @@
         <v>48</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1867,10 +1868,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>264</v>
@@ -1882,10 +1883,10 @@
         <v>49</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1893,10 +1894,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>264</v>
@@ -1908,10 +1909,10 @@
         <v>50</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1919,10 +1920,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>264</v>
@@ -1934,10 +1935,10 @@
         <v>51</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1945,10 +1946,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>264</v>
@@ -1960,10 +1961,10 @@
         <v>52</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1971,10 +1972,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>264</v>
@@ -1986,10 +1987,10 @@
         <v>53</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1997,10 +1998,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>264</v>
@@ -2012,10 +2013,10 @@
         <v>54</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -2023,10 +2024,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>264</v>
@@ -2038,21 +2039,21 @@
         <v>55</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>264</v>
@@ -2061,13 +2062,13 @@
         <v>35</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -2075,10 +2076,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>264</v>
@@ -2087,24 +2088,24 @@
         <v>35</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>264</v>
@@ -2113,13 +2114,13 @@
         <v>35</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -2127,10 +2128,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>264</v>
@@ -2139,13 +2140,13 @@
         <v>35</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -2153,10 +2154,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>264</v>
@@ -2165,13 +2166,13 @@
         <v>35</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2179,10 +2180,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>264</v>
@@ -2191,13 +2192,13 @@
         <v>35</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2205,10 +2206,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>264</v>
@@ -2217,13 +2218,13 @@
         <v>35</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -2231,10 +2232,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>264</v>
@@ -2243,24 +2244,24 @@
         <v>35</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>264</v>
@@ -2269,13 +2270,13 @@
         <v>35</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2283,10 +2284,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>264</v>
@@ -2295,13 +2296,13 @@
         <v>35</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2309,218 +2310,218 @@
         <v>29</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G32" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="H32" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="D33" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H35" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>191</v>
-      </c>
       <c r="D36" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>264</v>
@@ -2529,102 +2530,102 @@
         <v>35</v>
       </c>
       <c r="F40" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>222</v>
-      </c>
       <c r="C41" s="8" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>264</v>
@@ -2633,195 +2634,195 @@
         <v>35</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B45" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="D45" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="B48" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D48" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="B49" s="8" t="s">
+      <c r="C49" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="D49" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="B50" s="8" t="s">
+      <c r="C50" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="D50" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B51" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>176</v>
-      </c>
       <c r="D51" s="8" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>177</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
